--- a/document_templates/Материальный отчет_шаблон.xlsx
+++ b/document_templates/Материальный отчет_шаблон.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AISapp-mainnn\AISapp-main\document_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{260334CA-FE54-47B9-A680-A75060C33B6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75B52A29-3D81-4D34-B846-42E5F5EF3582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/document_templates/Материальный отчет_шаблон.xlsx
+++ b/document_templates/Материальный отчет_шаблон.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AISapp-mainnn\AISapp-main\document_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75B52A29-3D81-4D34-B846-42E5F5EF3582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAA23BBE-1555-4A71-A953-EC0ED21692AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>МАТЕРИАЛЬНЫЙ ОТЧЕТ № {{REPORT_NUMBER}}</t>
   </si>
@@ -84,12 +84,6 @@
     <t>Остаток на конец</t>
   </si>
   <si>
-    <t>Цена</t>
-  </si>
-  <si>
-    <t>Сумма остатка</t>
-  </si>
-  <si>
     <t>Документ-основание</t>
   </si>
   <si>
@@ -117,249 +111,12 @@
     <t>{{CLOSING_QTY}}</t>
   </si>
   <si>
-    <t>{{PRICE}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT}}</t>
-  </si>
-  <si>
     <t>{{BASIS_DOCUMENT}}</t>
   </si>
   <si>
-    <t>{{LINE_NO_2}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_CODE_2}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_2}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_2}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_2}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_2}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_2}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_2}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_2}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_2}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_2}}</t>
-  </si>
-  <si>
-    <t>{{LINE_NO_3}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_CODE_3}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_3}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_3}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_3}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_3}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_3}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_3}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_3}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_3}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_3}}</t>
-  </si>
-  <si>
     <t>Итого</t>
   </si>
   <si>
-    <t>{{MATERIAL_CODE_4}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_4}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_4}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_4}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_4}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_4}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_4}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_4}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_4}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_4}}</t>
-  </si>
-  <si>
-    <t>{{LINE_NO_4}}</t>
-  </si>
-  <si>
-    <t>{{LINE_NO_5}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_CODE_5}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_5}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_5}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_5}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_5}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_5}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_5}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_5}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_5}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_5}}</t>
-  </si>
-  <si>
-    <t>{{LINE_NO_6}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_CODE_6}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_6}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_6}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_6}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_6}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_6}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_6}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_6}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_6}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_6}}</t>
-  </si>
-  <si>
-    <t>{{LINE_NO_7}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_CODE_7}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_7}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_7}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_7}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_7}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_7}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_7}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_7}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_7}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_7}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_CODE_8}}</t>
-  </si>
-  <si>
-    <t>{{LINE_NO_8}}</t>
-  </si>
-  <si>
-    <t>{{MATERIAL_NAME_8}}</t>
-  </si>
-  <si>
-    <t>{{UNIT_8}}</t>
-  </si>
-  <si>
-    <t>{{OPENING_QTY_8}}</t>
-  </si>
-  <si>
-    <t>{{RECEIPT_QTY_8}}</t>
-  </si>
-  <si>
-    <t>{{ISSUE_QTY_8}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_QTY_8}}</t>
-  </si>
-  <si>
-    <t>{{PRICE_8}}</t>
-  </si>
-  <si>
-    <t>{{CLOSING_AMOUNT_8}}</t>
-  </si>
-  <si>
-    <t>{{BASIS_DOCUMENT_8}}</t>
-  </si>
-  <si>
     <t>{{TOTAL_OPENING}}</t>
   </si>
   <si>
@@ -370,9 +127,6 @@
   </si>
   <si>
     <t>{{TOTAL_CLOSING}}</t>
-  </si>
-  <si>
-    <t>{{TOTAL_AMOUNT}}</t>
   </si>
 </sst>
 </file>
@@ -776,22 +530,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="24.21875" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" customWidth="1"/>
     <col min="6" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="28" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -803,10 +555,8 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -820,7 +570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,7 +584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -862,335 +612,61 @@
       <c r="I6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="2" t="s">
+    </row>
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="7" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="3" t="s">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="G8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="H8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F16" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" t="s">
-        <v>111</v>
-      </c>
-      <c r="H16" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="J16" t="s">
-        <v>113</v>
-      </c>
-      <c r="K16" s="4"/>
+      <c r="I8" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A8:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
